--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46464EB-543D-4CE8-882C-150E8892DB90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E317A86A-074F-496B-9813-736848B0C420}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9690" yWindow="1605" windowWidth="17175" windowHeight="11865" activeTab="1" xr2:uid="{B7D5702C-2232-4DEE-919E-1C4D4E64D4F6}"/>
+    <workbookView xWindow="6750" yWindow="1560" windowWidth="17265" windowHeight="10470" xr2:uid="{B7D5702C-2232-4DEE-919E-1C4D4E64D4F6}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -556,5 +556,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E317A86A-074F-496B-9813-736848B0C420}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E88A1CE-6973-474C-B8B5-FDAA3C51379A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="1560" windowWidth="17265" windowHeight="10470" xr2:uid="{B7D5702C-2232-4DEE-919E-1C4D4E64D4F6}"/>
+    <workbookView xWindow="9195" yWindow="3330" windowWidth="13980" windowHeight="11385" activeTab="1" xr2:uid="{B7D5702C-2232-4DEE-919E-1C4D4E64D4F6}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -478,7 +478,7 @@
         <v>20</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -20,39 +20,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <x:si>
+    <x:t>monsterHP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>indexNum02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>monsterEXP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>monsterGold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>playerHP</x:t>
+  </x:si>
   <x:si>
     <x:t>attackRate</x:t>
   </x:si>
   <x:si>
-    <x:t>playerHP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>monsterEXP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>indexNum02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>monsterGold</x:t>
-  </x:si>
-  <x:si>
     <x:t>indexNum01</x:t>
   </x:si>
   <x:si>
-    <x:t>monsterHP</x:t>
+    <x:t>maxEXP</x:t>
   </x:si>
   <x:si>
     <x:t>addEXP</x:t>
   </x:si>
   <x:si>
+    <x:t>monsterSpeed</x:t>
+  </x:si>
+  <x:si>
     <x:t>attackDamage</x:t>
   </x:si>
   <x:si>
     <x:t>coolDownTime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>monsterSpeed</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -828,7 +831,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:F3"/>
+  <x:dimension ref="A1:G5"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.399999999999999"/>
   <x:cols>
     <x:col min="1" max="1" width="12.5" style="2" bestFit="1" customWidth="1"/>
@@ -840,27 +843,30 @@
     <x:col min="7" max="7" width="8.796875" style="1" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:7">
       <x:c r="A1" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="D1" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
     </x:row>
-    <x:row r="2" spans="1:6">
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="2">
         <x:v>1</x:v>
       </x:c>
@@ -879,14 +885,36 @@
       <x:c r="F2" s="2">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="G2" s="1">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
-    <x:row r="3" spans="1:1">
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="2">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="G3" s="1">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="2">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G4" s="1">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="2">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G5" s="1">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
@@ -906,16 +934,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>4</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
         <x:v>2</x:v>
@@ -944,7 +972,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,27 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300CD32D-B437-4BA4-B050-2B88D16E2BCF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6949B6AE-204F-47EC-AD6C-A97BFCA1E1D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="2130" windowWidth="15870" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="1665" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
     <sheet name="MonsterStatus" sheetId="2" r:id="rId2"/>
+    <sheet name="AttackType" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>monsterHP</t>
   </si>
   <si>
-    <t>indexNum02</t>
-  </si>
-  <si>
     <t>monsterEXP</t>
   </si>
   <si>
@@ -41,9 +39,6 @@
     <t>attackRate</t>
   </si>
   <si>
-    <t>indexNum01</t>
-  </si>
-  <si>
     <t>maxEXP</t>
   </si>
   <si>
@@ -57,13 +52,25 @@
   </si>
   <si>
     <t>coolDownTime</t>
+  </si>
+  <si>
+    <t>indexLevel02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indexLevel01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indexType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -72,6 +79,13 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -98,7 +112,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -106,6 +120,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -291,7 +308,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -300,7 +317,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -627,26 +644,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -742,20 +759,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -785,4 +802,119 @@
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6949B6AE-204F-47EC-AD6C-A97BFCA1E1D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4293B31-402C-4B40-9B7C-6F38EFE55892}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="1665" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="2415" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4293B31-402C-4B40-9B7C-6F38EFE55892}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ECBF33-1D27-40E3-8B25-A390A0CB319C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="2415" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="585" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -631,7 +631,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" style="2" bestFit="1" customWidth="1"/>
@@ -714,28 +714,211 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
       <c r="G6" s="2">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
       <c r="G7" s="2">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
       <c r="G8" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
       <c r="G9" s="2">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
       <c r="G10" s="2">
         <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="G12" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="G13" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="G17" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="G18" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="G19" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="G20" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="G21" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="G22" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="G23" s="2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="G24" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="G25" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="G26" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="G27" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="G28" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="G29" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="G30" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="G31" s="2">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87ECBF33-1D27-40E3-8B25-A390A0CB319C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC267E7-F9F7-4AD4-A6FD-5EF7C7EDDC37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="585" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7050" yWindow="2865" windowWidth="17940" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>monsterHP</t>
   </si>
@@ -63,6 +63,21 @@
   </si>
   <si>
     <t>indexType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monsterDamage</t>
+  </si>
+  <si>
+    <t>windSlash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterSlash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireSlash</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -112,7 +127,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -123,6 +138,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -671,19 +689,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>10</v>
@@ -693,6 +711,9 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
+      <c r="D3" s="2">
+        <v>0.1</v>
+      </c>
       <c r="G3" s="1">
         <v>15</v>
       </c>
@@ -701,6 +722,9 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
+      <c r="D4" s="2">
+        <v>0.2</v>
+      </c>
       <c r="G4" s="2">
         <v>20</v>
       </c>
@@ -709,6 +733,9 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
+      <c r="D5" s="2">
+        <v>0.3</v>
+      </c>
       <c r="G5" s="2">
         <v>25</v>
       </c>
@@ -717,6 +744,9 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
+      <c r="D6" s="2">
+        <v>0.4</v>
+      </c>
       <c r="G6" s="2">
         <v>30</v>
       </c>
@@ -725,6 +755,9 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
+      <c r="D7" s="2">
+        <v>0.5</v>
+      </c>
       <c r="G7" s="2">
         <v>35</v>
       </c>
@@ -733,6 +766,9 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
+      <c r="D8" s="2">
+        <v>0.6</v>
+      </c>
       <c r="G8" s="2">
         <v>40</v>
       </c>
@@ -741,6 +777,9 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
+      <c r="D9" s="2">
+        <v>0.7</v>
+      </c>
       <c r="G9" s="2">
         <v>45</v>
       </c>
@@ -749,6 +788,9 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
+      <c r="D10" s="2">
+        <v>0.8</v>
+      </c>
       <c r="G10" s="2">
         <v>50</v>
       </c>
@@ -757,6 +799,9 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
+      <c r="D11" s="2">
+        <v>0.9</v>
+      </c>
       <c r="G11" s="2">
         <v>55</v>
       </c>
@@ -764,6 +809,9 @@
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>60</v>
@@ -931,17 +979,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -957,143 +1006,127 @@
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <v>25</v>
       </c>
       <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>53</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC267E7-F9F7-4AD4-A6FD-5EF7C7EDDC37}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48A2BC2-54C5-4418-A100-6E0BD8EC6760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7050" yWindow="2865" windowWidth="17940" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9948" yWindow="2796" windowWidth="16452" windowHeight="11604" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -48,9 +48,6 @@
     <t>monsterSpeed</t>
   </si>
   <si>
-    <t>attackDamage</t>
-  </si>
-  <si>
     <t>coolDownTime</t>
   </si>
   <si>
@@ -78,6 +75,10 @@
   </si>
   <si>
     <t>fireSlash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerDamage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -127,20 +128,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,322 +642,322 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>0.2</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>0.3</v>
+      </c>
+      <c r="G5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>0.4</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>0.6</v>
+      </c>
+      <c r="G8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="D9">
+        <v>0.7</v>
+      </c>
+      <c r="G9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>0.8</v>
+      </c>
+      <c r="G10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>0.9</v>
+      </c>
+      <c r="G11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="D12">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="G12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="G16">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="G18">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="G19">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="G21">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="G23">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="G24">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="G25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.4</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="G26">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="G27">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="G28">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="G29">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="G30">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="G8" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="G9" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="G10" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="G11" s="2">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="G13" s="2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="G14" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="G15" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="G16" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="G17" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="G18" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="G19" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="G20" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="G21" s="2">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="G22" s="2">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="G23" s="2">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="G24" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="G25" s="2">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="G26" s="2">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="G27" s="2">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="G28" s="2">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="G29" s="2">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="G30" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="G31">
         <v>155</v>
       </c>
     </row>
@@ -980,73 +972,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C2">
+        <v>25</v>
+      </c>
+      <c r="D2">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2">
-        <v>25</v>
-      </c>
-      <c r="D2" s="2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6">
         <v>5</v>
       </c>
     </row>
@@ -1059,74 +1051,118 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B3">
+        <v>1.25</v>
+      </c>
+      <c r="C3">
+        <v>0.8</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="B4">
+        <v>1.5</v>
+      </c>
+      <c r="C4">
+        <v>0.7</v>
+      </c>
+      <c r="D4">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A5">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="B5">
+        <v>1.75</v>
+      </c>
+      <c r="C5">
+        <v>0.6</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0.5</v>
+      </c>
+      <c r="D6">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
+      <c r="B7">
+        <v>2.5</v>
+      </c>
+      <c r="C7">
+        <v>0.4</v>
+      </c>
+      <c r="D7">
+        <v>1.5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48A2BC2-54C5-4418-A100-6E0BD8EC6760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB939DA8-4C49-4DE9-96F6-1B7CAC563B65}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9948" yWindow="2796" windowWidth="16452" windowHeight="11604" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7530" yWindow="480" windowWidth="21600" windowHeight="13065" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t>monsterHP</t>
   </si>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>indexType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>monsterDamage</t>
   </si>
   <si>
@@ -79,6 +75,26 @@
   </si>
   <si>
     <t>playerDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weaponType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coolTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>typeAbility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>typeLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,18 +658,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -670,13 +686,13 @@
         <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -699,7 +715,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -710,7 +726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -721,7 +737,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -732,7 +748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -743,7 +759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -754,7 +770,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -765,7 +781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -776,7 +792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -787,7 +803,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -798,7 +814,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -809,7 +825,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -817,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -825,7 +841,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -833,7 +849,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -841,7 +857,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -849,7 +865,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -857,7 +873,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -865,7 +881,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -873,7 +889,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -881,7 +897,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -889,7 +905,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -897,7 +913,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -905,7 +921,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -913,7 +929,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -921,7 +937,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -929,7 +945,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -937,7 +953,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -945,7 +961,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -953,7 +969,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -972,17 +988,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -999,10 +1015,10 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1022,22 +1038,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1051,118 +1067,351 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2">
-        <v>0</v>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1.25</v>
       </c>
-      <c r="C3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>0.8</v>
       </c>
-      <c r="D3">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
         <v>1.5</v>
       </c>
-      <c r="C4">
-        <v>0.7</v>
-      </c>
-      <c r="D4">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>1.75</v>
-      </c>
-      <c r="C5">
-        <v>0.6</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>0.5</v>
-      </c>
-      <c r="D6">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>2.5</v>
-      </c>
-      <c r="C7">
-        <v>0.4</v>
-      </c>
-      <c r="D7">
-        <v>1.5</v>
-      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C20" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB939DA8-4C49-4DE9-96F6-1B7CAC563B65}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21691920-8505-4552-B275-D01223B4E994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7530" yWindow="480" windowWidth="21600" windowHeight="13065" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12012" yWindow="2328" windowWidth="16452" windowHeight="11604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -658,18 +658,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -692,12 +692,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>0.5</v>
@@ -715,7 +715,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -726,7 +726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -737,7 +737,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -748,7 +748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -759,7 +759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -770,7 +770,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -781,7 +781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -792,7 +792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -803,7 +803,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -814,7 +814,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -825,7 +825,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -841,7 +841,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -849,7 +849,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -857,7 +857,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -865,7 +865,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -873,7 +873,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -881,7 +881,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -889,7 +889,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -897,7 +897,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -905,7 +905,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -913,7 +913,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -921,7 +921,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -929,7 +929,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -937,7 +937,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -945,7 +945,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -953,7 +953,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -961,7 +961,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -969,7 +969,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -988,17 +988,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1038,22 +1038,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1068,21 +1068,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,7 +1104,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>0</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>0</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C20" s="1"/>
     </row>
   </sheetData>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21691920-8505-4552-B275-D01223B4E994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C80E05-B27B-4F57-A70F-1FEC944D919E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12012" yWindow="2328" windowWidth="16452" windowHeight="11604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5535" yWindow="2115" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -658,18 +658,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -692,12 +692,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>0.5</v>
@@ -715,7 +715,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -726,7 +726,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -737,7 +737,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -748,7 +748,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -759,7 +759,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -770,7 +770,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -781,7 +781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -792,7 +792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -803,7 +803,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -814,7 +814,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -825,7 +825,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -833,7 +833,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -841,7 +841,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -849,7 +849,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -857,7 +857,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -865,7 +865,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -873,7 +873,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -881,7 +881,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -889,7 +889,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -897,7 +897,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -905,7 +905,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -913,7 +913,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -921,7 +921,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -929,7 +929,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -937,7 +937,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -945,7 +945,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -953,7 +953,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -961,7 +961,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -969,7 +969,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -988,17 +988,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1038,22 +1038,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1068,21 +1068,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1104,7 +1104,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0</v>
       </c>
@@ -1189,7 +1189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1</v>
       </c>
@@ -1223,7 +1223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1257,7 +1257,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>2</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -1393,7 +1393,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
     </row>
   </sheetData>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C80E05-B27B-4F57-A70F-1FEC944D919E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45632B5D-147E-469B-9612-72801F7B95E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5535" yWindow="2115" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2520" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45632B5D-147E-469B-9612-72801F7B95E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C4228D-4773-4943-AC7A-49FE3BCFC37C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2520" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="2175" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>monsterHP</t>
   </si>
@@ -95,6 +95,10 @@
   </si>
   <si>
     <t>typeLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>indexUID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1070,12 +1074,12 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
@@ -1084,21 +1088,23 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -1111,306 +1117,360 @@
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>1.25</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>1.75</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
       <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
       <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
         <v>4</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
         <v>5</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>0.4</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
         <v>2</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
       <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
         <v>2</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>3</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
       <c r="E17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
         <v>2</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>4</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
       <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
         <v>2</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>5</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
       <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
     </row>
   </sheetData>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,21 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C4228D-4773-4943-AC7A-49FE3BCFC37C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3568FE3D-840A-44A8-BF15-E6CC83EB5E10}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="2175" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3270" yWindow="1620" windowWidth="21150" windowHeight="11925" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
     <sheet name="MonsterStatus" sheetId="2" r:id="rId2"/>
     <sheet name="AttackType" sheetId="3" r:id="rId3"/>
+    <sheet name="NomalAttack" sheetId="4" r:id="rId4"/>
+    <sheet name="SubSkill" sheetId="5" r:id="rId5"/>
+    <sheet name="MainSkill" sheetId="6" r:id="rId6"/>
+    <sheet name="PassiveSkill" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
   <si>
     <t>monsterHP</t>
   </si>
@@ -99,6 +103,106 @@
   </si>
   <si>
     <t>indexUID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerUID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monsterUID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>singleDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>spreadDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>spreadRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>speedDown</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drillDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>drillCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>penetDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>penetCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>barrierDuration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>barrierCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>windDrill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterBarrier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireBall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>windDuration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>attackSpeedUp</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterHeal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>explosionDamage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>explosionRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>windGusts</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>waterPurification</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireExplosion</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>subSkillUID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nomalAttackUID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -106,7 +210,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -124,6 +228,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -661,323 +772,417 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.5</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>0.1</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.2</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.3</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.4</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.5</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.6</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.7</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
         <v>9</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.8</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.9</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="G12">
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
         <v>12</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
         <v>13</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
         <v>14</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
         <v>15</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
         <v>16</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
         <v>17</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
         <v>18</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
         <v>19</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
         <v>20</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
         <v>21</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
         <v>22</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
         <v>23</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
         <v>24</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
         <v>25</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
         <v>26</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
         <v>27</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
         <v>28</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
         <v>29</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
         <v>30</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>155</v>
       </c>
     </row>
@@ -991,74 +1196,93 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
       <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
         <v>10</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>25</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>5</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>5</v>
       </c>
     </row>
@@ -1478,4 +1702,1361 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>1.25</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>1.5</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>1.75</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10">
+        <v>25</v>
+      </c>
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+      <c r="K12">
+        <v>3</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="K13">
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="I15">
+        <v>1.5</v>
+      </c>
+      <c r="J15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16">
+        <v>9</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17">
+        <v>8</v>
+      </c>
+      <c r="I17">
+        <v>2.5</v>
+      </c>
+      <c r="J17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18">
+        <v>7</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="I19">
+        <v>3.5</v>
+      </c>
+      <c r="J19">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10">
+        <v>80</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11">
+        <v>75</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12">
+        <v>70</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13">
+        <v>70</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>300</v>
+      </c>
+      <c r="K15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16">
+        <v>30</v>
+      </c>
+      <c r="J16">
+        <v>400</v>
+      </c>
+      <c r="K16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17">
+        <v>25</v>
+      </c>
+      <c r="J17">
+        <v>500</v>
+      </c>
+      <c r="K17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18">
+        <v>25</v>
+      </c>
+      <c r="J18">
+        <v>600</v>
+      </c>
+      <c r="K18">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+      <c r="J19">
+        <v>700</v>
+      </c>
+      <c r="K19">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3568FE3D-840A-44A8-BF15-E6CC83EB5E10}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B740F3-564C-4A52-9D0D-C5333E5B2EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3270" yWindow="1620" windowWidth="21150" windowHeight="11925" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9840" yWindow="2568" windowWidth="17496" windowHeight="11604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -773,19 +773,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -819,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0.5</v>
@@ -837,7 +837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -865,7 +865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -879,7 +879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -893,7 +893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -907,7 +907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -921,7 +921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -935,7 +935,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -949,7 +949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -963,7 +963,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -977,7 +977,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -988,7 +988,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -999,7 +999,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1197,18 +1197,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1296,21 +1296,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
@@ -1707,21 +1707,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="1" max="1" width="15.8984375" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.625" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.59765625" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2122,23 +2122,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2599,22 +2599,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.875" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.8984375" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3054,7 +3054,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B740F3-564C-4A52-9D0D-C5333E5B2EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FAD9F4-C4B9-4BC9-9885-65EC66FA5CF6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9840" yWindow="2568" windowWidth="17496" windowHeight="11604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4755" yWindow="1305" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -773,19 +773,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -822,7 +822,7 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -837,7 +837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -865,7 +865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -879,7 +879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -893,7 +893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -907,7 +907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -921,7 +921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -935,7 +935,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -949,7 +949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -963,7 +963,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -977,7 +977,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -988,7 +988,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -999,7 +999,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1197,18 +1197,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1296,21 +1296,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
@@ -1707,21 +1707,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.8984375" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.59765625" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2122,23 +2122,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.19921875" customWidth="1"/>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2599,22 +2599,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.8984375" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3054,7 +3054,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FAD9F4-C4B9-4BC9-9885-65EC66FA5CF6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169627A9-AF6D-4890-B006-2FFE36BB5226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="1305" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="2484" windowWidth="23196" windowHeight="11604" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -773,19 +773,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -811,7 +811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -837,7 +837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -851,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -865,7 +865,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -879,7 +879,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -893,7 +893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -907,7 +907,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -921,7 +921,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -935,7 +935,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -949,7 +949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -963,7 +963,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -977,7 +977,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -988,7 +988,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -999,7 +999,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1197,18 +1197,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1248,13 +1248,13 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1296,21 +1296,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1334,7 +1334,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
@@ -1707,21 +1707,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="1" max="1" width="15.8984375" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.625" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.59765625" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2122,23 +2122,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2599,22 +2599,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.875" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.8984375" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3054,7 +3054,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169627A9-AF6D-4890-B006-2FFE36BB5226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED9CD5C-776E-4B5F-98CB-3CA7E179116B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="2484" windowWidth="23196" windowHeight="11604" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8580" yWindow="1575" windowWidth="19020" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="48">
   <si>
     <t>monsterHP</t>
   </si>
@@ -199,6 +199,10 @@
   </si>
   <si>
     <t>subSkillUID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nomalAttackUID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -773,19 +777,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -811,7 +815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -837,7 +841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -851,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -865,7 +869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -879,7 +883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -893,7 +897,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -907,7 +911,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -921,7 +925,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -935,7 +939,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -949,7 +953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -963,7 +967,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -977,7 +981,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -988,7 +992,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -999,7 +1003,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1010,7 +1014,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1021,7 +1025,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1032,7 +1036,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1043,7 +1047,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1054,7 +1058,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1065,7 +1069,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1076,7 +1080,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1087,7 +1091,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1098,7 +1102,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1109,7 +1113,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1120,7 +1124,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1131,7 +1135,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1142,7 +1146,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1153,7 +1157,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1164,7 +1168,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1175,7 +1179,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1197,18 +1201,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1231,7 +1235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1254,7 +1258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1262,7 +1266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1270,7 +1274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1278,7 +1282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1296,21 +1300,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1334,7 +1338,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1354,7 +1358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1374,7 +1378,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1394,7 +1398,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1414,7 +1418,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1434,7 +1438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1454,7 +1458,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1474,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1494,7 +1498,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1514,7 +1518,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1534,7 +1538,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1554,7 +1558,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1574,7 +1578,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1594,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1614,7 +1618,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1634,7 +1638,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1654,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1674,7 +1678,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1694,7 +1698,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
@@ -1706,54 +1710,58 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.8984375" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.59765625" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1763,382 +1771,437 @@
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="G3">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="G4">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="H4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="G5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="H5">
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="G7">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="J9">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>0.2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="J10">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
         <v>3</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="J11">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="J12">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
         <v>5</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="J13">
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="K13">
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
         <v>3</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
         <v>4</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="H18">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C19">
+        <v>2</v>
+      </c>
+      <c r="D19">
         <v>5</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="H19">
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>1.5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.19921875" customWidth="1"/>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2176,7 +2239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2199,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2222,7 +2285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2245,7 +2308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2268,7 +2331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2291,7 +2354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2314,7 +2377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2337,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2360,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2383,7 +2446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2406,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2429,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2452,7 +2515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2475,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2498,7 +2561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2521,7 +2584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2544,7 +2607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2567,7 +2630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2599,22 +2662,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.8984375" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2649,7 +2712,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2672,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2695,7 +2758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2718,7 +2781,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2741,7 +2804,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2764,7 +2827,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2787,7 +2850,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2807,7 +2870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2827,7 +2890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2847,7 +2910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2867,7 +2930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2887,7 +2950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2907,7 +2970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2930,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2953,7 +3016,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2976,7 +3039,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2999,7 +3062,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3022,7 +3085,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3054,7 +3117,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED9CD5C-776E-4B5F-98CB-3CA7E179116B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F366863-E688-4201-B8D4-0B4E1F9D8377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8580" yWindow="1575" windowWidth="19020" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6036" yWindow="2568" windowWidth="23196" windowHeight="11604" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -777,19 +777,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -815,7 +815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -841,7 +841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -855,7 +855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -869,7 +869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -883,7 +883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -897,7 +897,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -911,7 +911,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -925,7 +925,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -939,7 +939,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -953,7 +953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -967,7 +967,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -981,7 +981,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -992,7 +992,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1113,7 +1113,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1201,18 +1201,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1300,21 +1300,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1338,7 +1338,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
@@ -1711,22 +1711,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.8984375" customWidth="1"/>
+    <col min="2" max="2" width="16.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1942,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1965,10 +1965,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1988,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2185,23 +2185,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2662,22 +2662,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.875" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.8984375" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3117,7 +3117,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F366863-E688-4201-B8D4-0B4E1F9D8377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9D8CB6-F162-4C5D-B23A-5983F6B2AFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6036" yWindow="2568" windowWidth="23196" windowHeight="11604" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8160" yWindow="1668" windowWidth="19800" windowHeight="11604" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.4">
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.4">
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.4">
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9D8CB6-F162-4C5D-B23A-5983F6B2AFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D5CA42-87CB-40BC-810E-14A79B80C82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8160" yWindow="1668" windowWidth="19800" windowHeight="11604" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5952" yWindow="2352" windowWidth="19800" windowHeight="11604" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -838,7 +838,7 @@
         <v>10</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
@@ -852,7 +852,7 @@
         <v>0.1</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
@@ -866,7 +866,7 @@
         <v>0.2</v>
       </c>
       <c r="H4">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -880,7 +880,7 @@
         <v>0.3</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
@@ -894,7 +894,7 @@
         <v>0.4</v>
       </c>
       <c r="H6">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -908,7 +908,7 @@
         <v>0.5</v>
       </c>
       <c r="H7">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
@@ -922,7 +922,7 @@
         <v>0.6</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
@@ -936,7 +936,7 @@
         <v>0.7</v>
       </c>
       <c r="H9">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
@@ -950,7 +950,7 @@
         <v>0.8</v>
       </c>
       <c r="H10">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
@@ -964,7 +964,7 @@
         <v>0.9</v>
       </c>
       <c r="H11">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
@@ -978,7 +978,7 @@
         <v>1</v>
       </c>
       <c r="H12">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -989,7 +989,7 @@
         <v>12</v>
       </c>
       <c r="H13">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -1000,7 +1000,7 @@
         <v>13</v>
       </c>
       <c r="H14">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
@@ -1011,7 +1011,7 @@
         <v>14</v>
       </c>
       <c r="H15">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
@@ -1022,7 +1022,7 @@
         <v>15</v>
       </c>
       <c r="H16">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -1033,7 +1033,7 @@
         <v>16</v>
       </c>
       <c r="H17">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
@@ -1044,7 +1044,7 @@
         <v>17</v>
       </c>
       <c r="H18">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
@@ -1055,7 +1055,7 @@
         <v>18</v>
       </c>
       <c r="H19">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
@@ -1066,7 +1066,7 @@
         <v>19</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -1077,7 +1077,7 @@
         <v>20</v>
       </c>
       <c r="H21">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -1088,7 +1088,7 @@
         <v>21</v>
       </c>
       <c r="H22">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
@@ -1099,7 +1099,7 @@
         <v>22</v>
       </c>
       <c r="H23">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -1110,7 +1110,7 @@
         <v>23</v>
       </c>
       <c r="H24">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
@@ -1121,7 +1121,7 @@
         <v>24</v>
       </c>
       <c r="H25">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
@@ -1132,7 +1132,7 @@
         <v>25</v>
       </c>
       <c r="H26">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="H27">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
@@ -1154,7 +1154,7 @@
         <v>27</v>
       </c>
       <c r="H28">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
@@ -1165,7 +1165,7 @@
         <v>28</v>
       </c>
       <c r="H29">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -1176,7 +1176,7 @@
         <v>29</v>
       </c>
       <c r="H30">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -1187,7 +1187,7 @@
         <v>30</v>
       </c>
       <c r="H31">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>25</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.4">
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.4">
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.4">
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.4">

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D5CA42-87CB-40BC-810E-14A79B80C82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3BEB32-8F09-4F01-8A7C-2E0FDEB0376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5952" yWindow="2352" windowWidth="19800" windowHeight="11604" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5952" yWindow="2352" windowWidth="19800" windowHeight="11604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3BEB32-8F09-4F01-8A7C-2E0FDEB0376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DDA0E4-B0C6-4AE5-82FA-300EA77FEE7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5952" yWindow="2352" windowWidth="19800" windowHeight="11604" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="55">
   <si>
     <t>monsterHP</t>
   </si>
@@ -207,6 +207,34 @@
   </si>
   <si>
     <t>nomalAttackUID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>typeExplanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적1명에게 {0}피해를 {0}번 입힌다 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}초간 {0}회 피격 데미지를 저항하는 방어막을 생성한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일직선으로 관통되는 강력한 공격을 시전한다. 맞은 적 전체 {0}피해</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더욱 강력한 일반 공격이 나간다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 공격 타격시 적의 접근 속도를 감소시킨다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 공격 타격시 범위 피해를 입힌다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -777,19 +805,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -815,7 +843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -841,7 +869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -855,7 +883,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -869,7 +897,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -883,7 +911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -897,7 +925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -911,7 +939,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -925,7 +953,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -939,7 +967,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -953,7 +981,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -967,7 +995,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -981,7 +1009,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -992,7 +1020,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1003,7 +1031,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1014,7 +1042,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1025,7 +1053,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1036,7 +1064,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1047,7 +1075,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1058,7 +1086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1069,7 +1097,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1080,7 +1108,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1091,7 +1119,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1102,7 +1130,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1113,7 +1141,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1124,7 +1152,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1135,7 +1163,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1146,7 +1174,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1157,7 +1185,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1168,7 +1196,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1179,7 +1207,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1201,18 +1229,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1235,7 +1263,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1258,7 +1286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1266,7 +1294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1274,7 +1302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1282,7 +1310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1300,21 +1328,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1338,7 +1366,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1358,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1378,7 +1406,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1398,7 +1426,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1418,7 +1446,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1438,7 +1466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1458,7 +1486,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1478,7 +1506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1498,7 +1526,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1518,7 +1546,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1538,7 +1566,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1558,7 +1586,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1578,7 +1606,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1598,7 +1626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1618,7 +1646,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1638,7 +1666,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1658,7 +1686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1678,7 +1706,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1698,7 +1726,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
@@ -1710,23 +1738,24 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
-  <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.8984375" customWidth="1"/>
-    <col min="2" max="2" width="16.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1760,8 +1789,11 @@
       <c r="K1" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1783,8 +1815,11 @@
       <c r="H2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1807,7 +1842,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1830,7 +1865,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1853,7 +1888,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1876,7 +1911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1899,7 +1934,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1921,8 +1956,11 @@
       <c r="K8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L8" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1945,7 +1983,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1968,7 +2006,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1991,7 +2029,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2014,7 +2052,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2037,7 +2075,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2059,8 +2097,11 @@
       <c r="I14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="L14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2083,7 +2124,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2106,7 +2147,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2129,7 +2170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2152,7 +2193,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2184,24 +2225,25 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.19921875" customWidth="1"/>
+    <col min="1" max="1" width="13.25" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.19921875" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2238,8 +2280,11 @@
       <c r="L1" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2261,8 +2306,11 @@
       <c r="H2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2285,7 +2333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2308,7 +2356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2331,7 +2379,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2354,7 +2402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2377,7 +2425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2399,8 +2447,11 @@
       <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2423,7 +2474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2446,7 +2497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2469,7 +2520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2492,7 +2543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2515,7 +2566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2537,8 +2588,11 @@
       <c r="J14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2561,7 +2615,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2584,7 +2638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2607,7 +2661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2630,7 +2684,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2656,28 +2710,29 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.8984375" customWidth="1"/>
-    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2712,7 +2767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2735,7 +2790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2758,7 +2813,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2781,7 +2836,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2804,7 +2859,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2827,7 +2882,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2850,7 +2905,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2870,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2890,7 +2945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2910,7 +2965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2930,7 +2985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2950,7 +3005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2970,7 +3025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2993,7 +3048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3016,7 +3071,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3039,7 +3094,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3062,7 +3117,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3085,7 +3140,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3117,7 +3172,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DDA0E4-B0C6-4AE5-82FA-300EA77FEE7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D4FC37-BE6E-4121-B0E0-631EAF05719B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="64">
   <si>
     <t>monsterHP</t>
   </si>
@@ -210,31 +210,67 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>typeExplanation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">적1명에게 {0}피해를 {0}번 입힌다 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{0}초간 {0}회 피격 데미지를 저항하는 방어막을 생성한다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일직선으로 관통되는 강력한 공격을 시전한다. 맞은 적 전체 {0}피해</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>더욱 강력한 일반 공격이 나간다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 공격 타격시 적의 접근 속도를 감소시킨다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 공격 타격시 범위 피해를 입힌다.</t>
+    <t>attackName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attackExplanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>바람 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>더욱 강력한 일반 공격이 나간다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 공격 타격시 적의 이동속도를 감소시킨다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불 속성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 공격을 맞출 시 범위 피해를 준다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subSkillName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subSkillExplanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윈드 드릴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 1명에세 피해를 6번 연속으로 입힌다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배리어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3초간 1회 피격 데미지를 저항하는 방어막을 생성한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파이어볼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일직선으로 관통되는 강력한 공격을 시전한다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1738,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.875" customWidth="1"/>
@@ -1752,10 +1788,11 @@
     <col min="9" max="9" width="14.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.375" customWidth="1"/>
+    <col min="12" max="12" width="12.75" customWidth="1"/>
+    <col min="14" max="14" width="32.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1792,8 +1829,11 @@
       <c r="L1" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1816,10 +1856,13 @@
         <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1842,7 +1885,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1865,7 +1908,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1888,7 +1931,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1911,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1934,7 +1977,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1957,10 +2000,13 @@
         <v>0</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1983,7 +2029,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2006,7 +2052,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2029,7 +2075,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2052,7 +2098,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2075,7 +2121,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2100,8 +2146,11 @@
       <c r="L14" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M14" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2124,7 +2173,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2225,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.25" customWidth="1"/>
@@ -2240,10 +2289,11 @@
     <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="35.75" customWidth="1"/>
+    <col min="13" max="13" width="14.625" customWidth="1"/>
+    <col min="14" max="14" width="47.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2281,10 +2331,13 @@
         <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2307,10 +2360,13 @@
         <v>0</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2333,7 +2389,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2356,7 +2412,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2379,7 +2435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2402,7 +2458,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2425,7 +2481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2448,10 +2504,13 @@
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2474,7 +2533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2497,7 +2556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2520,7 +2579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2543,7 +2602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2566,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2589,10 +2648,13 @@
         <v>0</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2615,7 +2677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GameSW\Documents\Project_Light\Assets\10.DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D4FC37-BE6E-4121-B0E0-631EAF05719B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE020E8-FC1B-4F8D-A6D4-9939D0F14222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -841,19 +841,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -879,7 +879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -905,7 +905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -919,7 +919,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -933,7 +933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -947,7 +947,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -961,7 +961,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -975,7 +975,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -989,7 +989,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1166,7 +1166,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1199,7 +1199,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1265,18 +1265,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1322,15 +1322,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1338,7 +1341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1346,7 +1349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1364,21 +1367,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B930B1B4-AA63-4BC5-9FDB-418299E833F1}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1402,7 +1405,7 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1422,7 +1425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1442,7 +1445,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1482,7 +1485,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1502,7 +1505,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1522,7 +1525,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1542,7 +1545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1562,7 +1565,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1582,7 +1585,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1602,7 +1605,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1622,7 +1625,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1642,7 +1645,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1662,7 +1665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1722,7 +1725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1742,7 +1745,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1762,7 +1765,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C20" s="1"/>
     </row>
   </sheetData>
@@ -1775,24 +1778,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D080F-923E-41A9-B35B-8C07CE585E79}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.8984375" customWidth="1"/>
+    <col min="2" max="2" width="16.09765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" customWidth="1"/>
-    <col min="14" max="14" width="32.125" customWidth="1"/>
+    <col min="9" max="9" width="14.69921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.69921875" customWidth="1"/>
+    <col min="14" max="14" width="32.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1833,7 +1836,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1862,7 +1865,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1885,7 +1888,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1908,7 +1911,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1931,7 +1934,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1977,7 +1980,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2006,7 +2009,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2029,7 +2032,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2052,7 +2055,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2075,7 +2078,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2121,7 +2124,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2150,7 +2153,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2173,7 +2176,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2196,7 +2199,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2219,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2242,7 +2245,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2275,25 +2278,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA41DA9-03F7-4CC6-8F98-0DA2C48348DF}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="13.19921875" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.25" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.19921875" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69921875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.625" customWidth="1"/>
-    <col min="14" max="14" width="47.125" customWidth="1"/>
+    <col min="13" max="13" width="14.59765625" customWidth="1"/>
+    <col min="14" max="14" width="47.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2337,7 +2340,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2366,7 +2369,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2389,7 +2392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2412,7 +2415,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2435,7 +2438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2458,7 +2461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2481,7 +2484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2510,7 +2513,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2533,7 +2536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2579,7 +2582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2602,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2625,7 +2628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2654,7 +2657,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2677,7 +2680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2700,7 +2703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2723,7 +2726,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2746,7 +2749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2779,22 +2782,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EB7882-5E9B-405E-8507-BD6A4C9E299A}">
   <dimension ref="A1:K19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.875" customWidth="1"/>
-    <col min="5" max="5" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.8984375" customWidth="1"/>
+    <col min="5" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -2829,7 +2832,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2852,7 +2855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2875,7 +2878,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2898,7 +2901,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2921,7 +2924,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2967,7 +2970,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2987,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -3027,7 +3030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -3047,7 +3050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -3067,7 +3070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -3087,7 +3090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -3110,7 +3113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -3133,7 +3136,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -3156,7 +3159,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -3179,7 +3182,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -3202,7 +3205,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -3234,7 +3237,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609EF367-8FE0-4AFF-8B41-6A4FFCE31DE5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE020E8-FC1B-4F8D-A6D4-9939D0F14222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E3CADF-A818-4527-ACA3-B913F7CF1C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E3CADF-A818-4527-ACA3-B913F7CF1C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345DC876-30B2-473C-9FE9-72484DCA8B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3576" yWindow="1632" windowWidth="23856" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>0.25</v>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345DC876-30B2-473C-9FE9-72484DCA8B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C0277E-51CE-4328-AFE5-D948AEC081DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3576" yWindow="1632" windowWidth="23856" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>0.25</v>

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C0277E-51CE-4328-AFE5-D948AEC081DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E1FF15-5493-4B2D-A237-A5E8546BEE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3576" yWindow="1632" windowWidth="23856" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -254,10 +254,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>적 1명에세 피해를 6번 연속으로 입힌다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>배리어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -271,6 +267,10 @@
   </si>
   <si>
     <t>일직선으로 관통되는 강력한 공격을 시전한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 1명에게 피해를 6번 연속으로 입힌다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2366,7 +2366,7 @@
         <v>58</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -2507,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.4">
@@ -2651,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.4">

--- a/Assets/10.DataTable/DB_Status.xlsx
+++ b/Assets/10.DataTable/DB_Status.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityGameProject\Project_Light\Assets\10.DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E1FF15-5493-4B2D-A237-A5E8546BEE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5F0852-6D4C-4B1E-BB93-86BBDD064D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3312" yWindow="2148" windowWidth="23856" windowHeight="12120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="1" r:id="rId1"/>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
